--- a/data/trending_integrated_20261028_14.xlsx
+++ b/data/trending_integrated_20261028_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>151116754696</v>
+        <v>151153070811</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>주가 급등에 대한 기대감과 연상 가능성 언급. 과거 부실 기업 이미지에서 벗어나는 모습.</t>
+          <t>빛과전자, 상한가 기록 후 연상 기대감. 과거 쓰레기 회사에서 벗어나 긍정적 주가 흐름 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['급등', '연상']</t>
+          <t>['상한가', '연상', '주가흐름']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,7 +643,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27750</v>
+        <v>18790</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.84%</t>
+          <t>'+18.70%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.15</v>
+        <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>239</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="G3" t="n">
-        <v>263</v>
+        <v>401</v>
       </c>
       <c r="H3" t="n">
-        <v>5.16</v>
+        <v>1.11</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,91 +687,91 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>23750</v>
+        <v>15830</v>
       </c>
       <c r="K3" t="n">
-        <v>24200</v>
+        <v>17170</v>
       </c>
       <c r="L3" t="n">
-        <v>29900</v>
+        <v>19800</v>
       </c>
       <c r="M3" t="n">
-        <v>24200</v>
+        <v>15830</v>
       </c>
       <c r="N3" t="n">
-        <v>5.31</v>
+        <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>170115785150</v>
+        <v>342893932975</v>
       </c>
       <c r="P3" t="n">
-        <v>50600</v>
+        <v>28800</v>
       </c>
       <c r="Q3" t="n">
-        <v>13210</v>
+        <v>11550</v>
       </c>
       <c r="R3" t="n">
-        <v>6000</v>
+        <v>-84000</v>
       </c>
       <c r="S3" t="n">
-        <v>227000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>원익홀딩스, 로봇 관련주로 주목받으며 기대감 형성. 다만, 구체적인 호재보다는 기대감에 따른 변동성 언급.</t>
+          <t>멜콘, 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스. 3만, 10만 목표 주가 언급하며 기대감 고조.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇', '품절주', '인수']</t>
+          <t>['반도체장비', '공급망', '목표주가']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18170</v>
+        <v>27950</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.78%</t>
+          <t>'+17.68%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.02</v>
+        <v>-0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>230</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>389</v>
+        <v>269</v>
       </c>
       <c r="H4" t="n">
-        <v>1.11</v>
+        <v>5.16</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,60 +779,60 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15830</v>
+        <v>23750</v>
       </c>
       <c r="K4" t="n">
-        <v>17170</v>
+        <v>24200</v>
       </c>
       <c r="L4" t="n">
-        <v>19800</v>
+        <v>29900</v>
       </c>
       <c r="M4" t="n">
-        <v>15830</v>
+        <v>24200</v>
       </c>
       <c r="N4" t="n">
-        <v>0.09</v>
+        <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>334914418175</v>
+        <v>171528762850</v>
       </c>
       <c r="P4" t="n">
-        <v>28800</v>
+        <v>50600</v>
       </c>
       <c r="Q4" t="n">
-        <v>11550</v>
+        <v>13210</v>
       </c>
       <c r="R4" t="n">
-        <v>-84000</v>
+        <v>6000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>227000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>뉴스 기반 긍정적 전망. 반도체 공급망 진입 및 주요 기업 협력 기대.</t>
+          <t>원익홀딩스, 로봇 관련주로 주목받으며 기대감 형성. 다만, 구체적인 호재보다는 기대감에 따른 변동성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['마이크론', '반도체 장비', '공급망']</t>
+          <t>['로봇', '품절주', '인수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>189700</v>
+        <v>190400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.87%</t>
+          <t>'+11.28%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="H5" t="n">
         <v>74.90000000000001</v>
@@ -877,7 +877,7 @@
         <v>176300</v>
       </c>
       <c r="L5" t="n">
-        <v>190100</v>
+        <v>190800</v>
       </c>
       <c r="M5" t="n">
         <v>175400</v>
@@ -886,7 +886,7 @@
         <v>74.89</v>
       </c>
       <c r="O5" t="n">
-        <v>660987543800</v>
+        <v>680893248700</v>
       </c>
       <c r="P5" t="n">
         <v>243500</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1473000</v>
+        <v>1482000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.84%</t>
+          <t>'+10.51%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G6" t="n">
-        <v>1894</v>
+        <v>1877</v>
       </c>
       <c r="H6" t="n">
         <v>48.61</v>
@@ -978,7 +978,7 @@
         <v>48.66</v>
       </c>
       <c r="O6" t="n">
-        <v>4306685946500</v>
+        <v>4395781981500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>4분기 실적 기대감과 저평가 논리에 기반한 매수세 유입 전망. 해외 공급망 관련 뉴스 주목.</t>
+          <t>SK하이닉스, 4분기 100조 실적 기대감. 200, 400 목표 언급하며 주가 상승 기대감 높아짐.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적 기대', '저평가', '공급망']</t>
+          <t>['실적기대', '주가상승', '목표주가']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14950</v>
+        <v>14990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.12%</t>
+          <t>'+9.42%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="H7" t="n">
         <v>2.87</v>
@@ -1070,7 +1070,7 @@
         <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>165806644645</v>
+        <v>167022980660</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>240500</v>
+        <v>241750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.33%</t>
+          <t>'+8.90%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="G8" t="n">
-        <v>1632</v>
+        <v>1682</v>
       </c>
       <c r="H8" t="n">
         <v>46.15</v>
@@ -1162,7 +1162,7 @@
         <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2906668450750</v>
+        <v>2974825032750</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>일부 긍정적 기대감에도 불구하고 객관적 근거 부족. 외인 비중 변화 미미.</t>
+          <t>삼성전자, 3분기 순이익 115조 예상 언급. 자사주 소각 공시 기대감 있으나, 실제 발표 내용에 따라 변동 가능성 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['성과급', '20선', '100만 전자']</t>
+          <t>['순이익', '자사주소각', '실적발표']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18430</v>
+        <v>18490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.84%</t>
+          <t>'+8.19%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>72</v>
       </c>
       <c r="G9" t="n">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="H9" t="n">
         <v>4.74</v>
@@ -1254,7 +1254,7 @@
         <v>4.13</v>
       </c>
       <c r="O9" t="n">
-        <v>45802712980</v>
+        <v>45996075790</v>
       </c>
       <c r="P9" t="n">
         <v>28600</v>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18910</v>
+        <v>19300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+5.70%</t>
+          <t>'+7.88%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
         <v>112</v>
@@ -1346,7 +1346,7 @@
         <v>3.79</v>
       </c>
       <c r="O10" t="n">
-        <v>68339817450</v>
+        <v>69106237475</v>
       </c>
       <c r="P10" t="n">
         <v>22450</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2580</v>
+        <v>8690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+5.31%</t>
+          <t>'+5.98%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.68</v>
+        <v>0.27</v>
       </c>
       <c r="E11" t="n">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="F11" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G11" t="n">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="H11" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2450</v>
+        <v>8200</v>
       </c>
       <c r="K11" t="n">
-        <v>2525</v>
+        <v>8230</v>
       </c>
       <c r="L11" t="n">
+        <v>9780</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8100</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O11" t="n">
+        <v>123069017150</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9820</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2965</v>
       </c>
-      <c r="M11" t="n">
-        <v>2505</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O11" t="n">
-        <v>84658647479</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2965</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>865</v>
-      </c>
       <c r="R11" t="n">
-        <v>-365000</v>
+        <v>-67000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>거래량 증가 및 개인 물량 흡수 기반 반등 기대. 전환사채 및 전환 이슈 존재.</t>
+          <t>미국 양자/보안주 급등 및 국내 해킹 사고 관련, 보안 테마 상승 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['거래량', '반등 기대', '전환사채']</t>
+          <t>['보안', '해킹', '테마']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8590</v>
+        <v>2575</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.76%</t>
+          <t>'+5.10%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.27</v>
+        <v>0.68</v>
       </c>
       <c r="E12" t="n">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="F12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12" t="n">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="H12" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8200</v>
+        <v>2450</v>
       </c>
       <c r="K12" t="n">
-        <v>8230</v>
+        <v>2525</v>
       </c>
       <c r="L12" t="n">
-        <v>9780</v>
+        <v>2965</v>
       </c>
       <c r="M12" t="n">
-        <v>8100</v>
+        <v>2505</v>
       </c>
       <c r="N12" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>122205684300</v>
+        <v>85297084682</v>
       </c>
       <c r="P12" t="n">
-        <v>9820</v>
+        <v>2965</v>
       </c>
       <c r="Q12" t="n">
-        <v>2965</v>
+        <v>865</v>
       </c>
       <c r="R12" t="n">
-        <v>-67000</v>
+        <v>-365000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 양자/보안주 급등 및 국내 해킹 사고 관련, 보안 테마 상승 기대.</t>
+          <t>거래량 증가 및 개인 물량 흡수 기반 반등 기대. 전환사채 및 전환 이슈 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '테마']</t>
+          <t>['거래량', '반등 기대', '전환사채']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64600</v>
+        <v>64500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.86%</t>
+          <t>'+3.70%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.57</v>
       </c>
       <c r="E13" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G13" t="n">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="H13" t="n">
         <v>41.01</v>
@@ -1622,7 +1622,7 @@
         <v>40.44</v>
       </c>
       <c r="O13" t="n">
-        <v>214495183650</v>
+        <v>217195662500</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>최근 수익률 1위 달성과 자사주 매입 계획을 기반으로 한 긍정적 주가 전망.</t>
+          <t>삼성E&amp;A, 최근 코스피 수익률 1위 달성. 자사주 매입 진행 중이며, 10만원 목표 기대감 상승.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수익률 1위', '자사주 매입']</t>
+          <t>['수익률', '자사주매입', '목표가']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>179400</v>
+        <v>178500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.93%</t>
+          <t>'+2.41%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>757</v>
+        <v>783</v>
       </c>
       <c r="F14" t="n">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="G14" t="n">
-        <v>2614</v>
+        <v>2692</v>
       </c>
       <c r="H14" t="n">
         <v>35.43</v>
@@ -1708,13 +1708,13 @@
         <v>186900</v>
       </c>
       <c r="M14" t="n">
-        <v>179200</v>
+        <v>178400</v>
       </c>
       <c r="N14" t="n">
         <v>35.49</v>
       </c>
       <c r="O14" t="n">
-        <v>146221403250</v>
+        <v>151929950900</v>
       </c>
       <c r="P14" t="n">
         <v>304000</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30050</v>
+        <v>29975</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.86%</t>
+          <t>'+1.61%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F15" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G15" t="n">
-        <v>545</v>
+        <v>564</v>
       </c>
       <c r="H15" t="n">
         <v>28.81</v>
@@ -1806,7 +1806,7 @@
         <v>28.82</v>
       </c>
       <c r="O15" t="n">
-        <v>30508114950</v>
+        <v>31370363625</v>
       </c>
       <c r="P15" t="n">
         <v>69700</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>카카오 주가 하락 및 변동성에 대한 부정적 전망과 기대감이 혼재. 일부는 3만원 이하 하락을 예상하며 비판적인 태도를 보임.</t>
+          <t>카카오, 3만원 돌파 후에도 부정적 전망. 전환사채 및 스톡옵션 발행 조사 필요성 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['물타기', '공매도', '전환사채']</t>
+          <t>['전환사채', '스톡옵션', '부정적전망']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16490</v>
+        <v>16470</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.61%</t>
+          <t>'+0.49%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F16" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G16" t="n">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="H16" t="n">
         <v>28.03</v>
@@ -1898,7 +1898,7 @@
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>51055485675</v>
+        <v>52527398035</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주문량 대비 주가 하락, 애널리스트 및 증권사 비판. 부정적 논조.</t>
+          <t>삼성중공업, 주문량 대비 주가 하락에 대한 불만 제기. 실적 발표 후에도 주가 흐름 미미.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가', '실적발표']</t>
+          <t>['주문량', '실적발표', '주가하락']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52500</v>
+        <v>52400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.94%</t>
+          <t>'-1.13%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,7 +1961,7 @@
         <v>474</v>
       </c>
       <c r="F17" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G17" t="n">
         <v>1252</v>
@@ -1990,7 +1990,7 @@
         <v>10.34</v>
       </c>
       <c r="O17" t="n">
-        <v>76828950100</v>
+        <v>77489393800</v>
       </c>
       <c r="P17" t="n">
         <v>154800</v>
@@ -2035,70 +2035,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2130</v>
+        <v>14230</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.84%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="F18" t="n">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="G18" t="n">
-        <v>306</v>
+        <v>606</v>
       </c>
       <c r="H18" t="n">
-        <v>5.07</v>
+        <v>9.83</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2170</v>
+        <v>14450</v>
       </c>
       <c r="K18" t="n">
-        <v>2160</v>
+        <v>14750</v>
       </c>
       <c r="L18" t="n">
-        <v>2475</v>
+        <v>14870</v>
       </c>
       <c r="M18" t="n">
-        <v>2120</v>
+        <v>14090</v>
       </c>
       <c r="N18" t="n">
-        <v>4.89</v>
+        <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>49016261904</v>
+        <v>60996725455</v>
       </c>
       <c r="P18" t="n">
-        <v>4980</v>
+        <v>40350</v>
       </c>
       <c r="Q18" t="n">
-        <v>774</v>
+        <v>3320</v>
       </c>
       <c r="R18" t="n">
-        <v>-105000</v>
+        <v>-873000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-85000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세에도 불구하고 주가 흐름 둔화. 보호예수 해제 및 불확실성 존재.</t>
+          <t>코스피 지수 대비 마이너스, 상폐 및 사기꾼 등 강한 부정적 감정 표출. 객관적 근거 부재.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,51 +2107,51 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['로봇 섹터', '보호예수', '주가 흐름']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK증권</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14170</v>
+        <v>2015</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-1.94%</t>
+          <t>'-3.36%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.19</v>
+        <v>0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>260</v>
+        <v>90</v>
       </c>
       <c r="F19" t="n">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="G19" t="n">
-        <v>598</v>
+        <v>119</v>
       </c>
       <c r="H19" t="n">
-        <v>9.83</v>
+        <v>2.52</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14450</v>
+        <v>2085</v>
       </c>
       <c r="K19" t="n">
-        <v>14750</v>
+        <v>2005</v>
       </c>
       <c r="L19" t="n">
-        <v>14870</v>
+        <v>2025</v>
       </c>
       <c r="M19" t="n">
-        <v>14090</v>
+        <v>1805</v>
       </c>
       <c r="N19" t="n">
-        <v>10.02</v>
+        <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>59481467985</v>
+        <v>15499875971</v>
       </c>
       <c r="P19" t="n">
-        <v>40350</v>
+        <v>6190</v>
       </c>
       <c r="Q19" t="n">
-        <v>3320</v>
+        <v>636</v>
       </c>
       <c r="R19" t="n">
-        <v>-873000</v>
+        <v>-1333000</v>
       </c>
       <c r="S19" t="n">
-        <v>-85000</v>
+        <v>19000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>코스피 지수 대비 마이너스, 상폐 및 사기꾼 등 강한 부정적 감정 표출. 객관적 근거 부재.</t>
+          <t>SK하이닉스 연계 호재 언급 있으나, 액면병합 및 공매도 관련 부정적 논조.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,90 +2199,90 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['SK하이닉스', '공매도', '액면병합']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>001510</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2005</v>
+        <v>2085</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.84%</t>
+          <t>'-3.92%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.39</v>
+        <v>0.18</v>
       </c>
       <c r="E20" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G20" t="n">
-        <v>118</v>
+        <v>323</v>
       </c>
       <c r="H20" t="n">
-        <v>2.52</v>
+        <v>5.07</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
+        <v>2170</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2160</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2475</v>
+      </c>
+      <c r="M20" t="n">
         <v>2085</v>
       </c>
-      <c r="K20" t="n">
-        <v>2005</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1805</v>
-      </c>
       <c r="N20" t="n">
-        <v>2.13</v>
+        <v>4.89</v>
       </c>
       <c r="O20" t="n">
-        <v>15301300926</v>
+        <v>50028268578</v>
       </c>
       <c r="P20" t="n">
-        <v>6190</v>
+        <v>4980</v>
       </c>
       <c r="Q20" t="n">
-        <v>636</v>
+        <v>774</v>
       </c>
       <c r="R20" t="n">
-        <v>-1333000</v>
+        <v>-105000</v>
       </c>
       <c r="S20" t="n">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>SK하이닉스 연계 호재 언급 있으나, 액면병합 및 공매도 관련 부정적 논조.</t>
+          <t>로봇 섹터 강세에도 불구하고 주가 흐름 둔화. 보호예수 해제 및 불확실성 존재.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '공매도', '액면병합']</t>
+          <t>['로봇 섹터', '보호예수', '주가 흐름']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>001510</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9010</v>
+        <v>9040</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.46%</t>
+          <t>'-5.14%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.83</v>
       </c>
       <c r="E21" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="H21" t="n">
         <v>3.46</v>
@@ -2358,7 +2358,7 @@
         <v>2.63</v>
       </c>
       <c r="O21" t="n">
-        <v>43928111380</v>
+        <v>44411972320</v>
       </c>
       <c r="P21" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261028_14.xlsx
+++ b/data/trending_integrated_20261028_14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F2" t="n">
         <v>84</v>
       </c>
       <c r="G2" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>151153070811</v>
+        <v>151204283371</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -619,7 +619,7 @@
         <v>592</v>
       </c>
       <c r="R2" t="n">
-        <v>1208000</v>
+        <v>1108000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18790</v>
+        <v>27800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.70%</t>
+          <t>'+17.05%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.02</v>
+        <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>239</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>401</v>
+        <v>270</v>
       </c>
       <c r="H3" t="n">
-        <v>1.11</v>
+        <v>5.16</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,91 +687,91 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>15830</v>
+        <v>23750</v>
       </c>
       <c r="K3" t="n">
-        <v>17170</v>
+        <v>24200</v>
       </c>
       <c r="L3" t="n">
-        <v>19800</v>
+        <v>29900</v>
       </c>
       <c r="M3" t="n">
-        <v>15830</v>
+        <v>24200</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09</v>
+        <v>5.31</v>
       </c>
       <c r="O3" t="n">
-        <v>342893932975</v>
+        <v>172407391000</v>
       </c>
       <c r="P3" t="n">
-        <v>28800</v>
+        <v>50600</v>
       </c>
       <c r="Q3" t="n">
-        <v>11550</v>
+        <v>13210</v>
       </c>
       <c r="R3" t="n">
-        <v>-84000</v>
+        <v>-27000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>219000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>멜콘, 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스. 3만, 10만 목표 주가 언급하며 기대감 고조.</t>
+          <t>원익홀딩스, 로봇 관련주로 주목받으며 기대감 형성. 다만, 구체적인 호재보다는 기대감에 따른 변동성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체장비', '공급망', '목표주가']</t>
+          <t>['로봇', '품절주', '인수']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27950</v>
+        <v>18410</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.68%</t>
+          <t>'+16.30%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.15</v>
+        <v>1.02</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>242</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="G4" t="n">
-        <v>269</v>
+        <v>398</v>
       </c>
       <c r="H4" t="n">
-        <v>5.16</v>
+        <v>1.11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,60 +779,60 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>23750</v>
+        <v>15830</v>
       </c>
       <c r="K4" t="n">
-        <v>24200</v>
+        <v>17170</v>
       </c>
       <c r="L4" t="n">
-        <v>29900</v>
+        <v>19800</v>
       </c>
       <c r="M4" t="n">
-        <v>24200</v>
+        <v>15830</v>
       </c>
       <c r="N4" t="n">
-        <v>5.31</v>
+        <v>0.09</v>
       </c>
       <c r="O4" t="n">
-        <v>171528762850</v>
+        <v>346288826145</v>
       </c>
       <c r="P4" t="n">
-        <v>50600</v>
+        <v>28800</v>
       </c>
       <c r="Q4" t="n">
-        <v>13210</v>
+        <v>11550</v>
       </c>
       <c r="R4" t="n">
-        <v>6000</v>
+        <v>-87000</v>
       </c>
       <c r="S4" t="n">
-        <v>227000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>원익홀딩스, 로봇 관련주로 주목받으며 기대감 형성. 다만, 구체적인 호재보다는 기대감에 따른 변동성 언급.</t>
+          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스, 삼성전자·하이닉스·마이크론 등 빅테크 협력사 관련 긍정적 전망. 4분기 공급 가시화.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', '품절주', '인수']</t>
+          <t>['마이크론', 'ASML', '반도체 장비']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>190400</v>
+        <v>190350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.28%</t>
+          <t>'+11.25%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G5" t="n">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="H5" t="n">
         <v>74.90000000000001</v>
@@ -886,7 +886,7 @@
         <v>74.89</v>
       </c>
       <c r="O5" t="n">
-        <v>680893248700</v>
+        <v>691847062250</v>
       </c>
       <c r="P5" t="n">
         <v>243500</v>
@@ -895,10 +895,10 @@
         <v>71000</v>
       </c>
       <c r="R5" t="n">
-        <v>1006000</v>
+        <v>1017000</v>
       </c>
       <c r="S5" t="n">
-        <v>-20000</v>
+        <v>-28000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1482000</v>
+        <v>1486000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.51%</t>
+          <t>'+10.81%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="G6" t="n">
-        <v>1877</v>
+        <v>1813</v>
       </c>
       <c r="H6" t="n">
         <v>48.61</v>
@@ -978,7 +978,7 @@
         <v>48.66</v>
       </c>
       <c r="O6" t="n">
-        <v>4395781981500</v>
+        <v>4495463249500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -987,14 +987,14 @@
         <v>501000</v>
       </c>
       <c r="R6" t="n">
-        <v>120000</v>
+        <v>285000</v>
       </c>
       <c r="S6" t="n">
-        <v>228000</v>
+        <v>211000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>SK하이닉스, 4분기 100조 실적 기대감. 200, 400 목표 언급하며 주가 상승 기대감 높아짐.</t>
+          <t>4분기 실적 100조 예상 및 반도체 2차 랠리 시작 기대감으로 강한 상승세 전망. 개인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적기대', '주가상승', '목표주가']</t>
+          <t>['4분기 실적', '반도체 랠리', '개인 매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14990</v>
+        <v>15040</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.42%</t>
+          <t>'+9.78%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G7" t="n">
-        <v>616</v>
+        <v>642</v>
       </c>
       <c r="H7" t="n">
         <v>2.87</v>
@@ -1070,7 +1070,7 @@
         <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>167022980660</v>
+        <v>168596287900</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1079,23 +1079,23 @@
         <v>1760</v>
       </c>
       <c r="R7" t="n">
-        <v>294000</v>
+        <v>338000</v>
       </c>
       <c r="S7" t="n">
-        <v>16000</v>
+        <v>21000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>국민연금 및 외국인 프로그램 적극 매수 속에서 메타, 광통신 섹터 호재 기반 2만원 돌파 및 2만 이상 분할매수 권유. 공매도 언급.</t>
+          <t>국민연금 매수 및 외국인 프로그램 매수세 집중, 미래 기술 Seed 전략 수립 관련 기대감으로 강한 상승세 전망. 공매도 압박.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외국인 프로그램', '메타', '공매도']</t>
+          <t>['국민연금', '외국인 프로그램', '미래 기술']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>241750</v>
+        <v>242250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.90%</t>
+          <t>'+9.12%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G8" t="n">
-        <v>1682</v>
+        <v>1639</v>
       </c>
       <c r="H8" t="n">
         <v>46.15</v>
@@ -1162,7 +1162,7 @@
         <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2974825032750</v>
+        <v>3056771873250</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1171,14 +1171,14 @@
         <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>1368000</v>
+        <v>1511000</v>
       </c>
       <c r="S8" t="n">
-        <v>1139000</v>
+        <v>1136000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성전자, 3분기 순이익 115조 예상 언급. 자사주 소각 공시 기대감 있으나, 실제 발표 내용에 따라 변동 가능성 존재.</t>
+          <t>노무라 증권 목표가 하향에도 불구하고, 3분기 예상 순이익 전망 및 자사주 소각 기대감으로 단기 상승 기대. 단, 감정적 표현 다수.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['순이익', '자사주소각', '실적발표']</t>
+          <t>['노무라 증권', '자사주 소각', '실적 전망']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18490</v>
+        <v>19400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.19%</t>
+          <t>'+8.44%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
       <c r="E9" t="n">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>382</v>
+        <v>112</v>
       </c>
       <c r="H9" t="n">
-        <v>4.74</v>
+        <v>4.25</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17090</v>
+        <v>17890</v>
       </c>
       <c r="K9" t="n">
-        <v>19270</v>
+        <v>18250</v>
       </c>
       <c r="L9" t="n">
-        <v>20450</v>
+        <v>20000</v>
       </c>
       <c r="M9" t="n">
-        <v>18070</v>
+        <v>17950</v>
       </c>
       <c r="N9" t="n">
-        <v>4.13</v>
+        <v>3.79</v>
       </c>
       <c r="O9" t="n">
-        <v>45996075790</v>
+        <v>70145984045</v>
       </c>
       <c r="P9" t="n">
-        <v>28600</v>
+        <v>22450</v>
       </c>
       <c r="Q9" t="n">
-        <v>11050</v>
+        <v>6320</v>
       </c>
       <c r="R9" t="n">
-        <v>-55000</v>
+        <v>-7000</v>
       </c>
       <c r="S9" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 데이터센터 방열 시스템 공급 계약 체결 및 휴머노이드 로봇 관련 호재. 글로벌 대호재 2개 존재.</t>
+          <t>국내외 해킹 사고 연이은 발생, 양자보안 의무화 등 보안 섹터 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '로봇', '공급 계약']</t>
+          <t>['보안', '해킹', '양자보안']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19300</v>
+        <v>18380</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.88%</t>
+          <t>'+7.55%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="E10" t="n">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="G10" t="n">
-        <v>112</v>
+        <v>397</v>
       </c>
       <c r="H10" t="n">
-        <v>4.25</v>
+        <v>4.74</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17890</v>
+        <v>17090</v>
       </c>
       <c r="K10" t="n">
-        <v>18250</v>
+        <v>19270</v>
       </c>
       <c r="L10" t="n">
-        <v>20000</v>
+        <v>20450</v>
       </c>
       <c r="M10" t="n">
-        <v>17950</v>
+        <v>18070</v>
       </c>
       <c r="N10" t="n">
-        <v>3.79</v>
+        <v>4.13</v>
       </c>
       <c r="O10" t="n">
-        <v>69106237475</v>
+        <v>46136697450</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>28600</v>
       </c>
       <c r="Q10" t="n">
-        <v>6320</v>
+        <v>11050</v>
       </c>
       <c r="R10" t="n">
-        <v>-23000</v>
+        <v>-59000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>국내외 해킹 사고 연이은 발생, 양자보안 의무화 등 보안 섹터 상승 기대.</t>
+          <t>AI 데이터센터 방열 시스템 공급 계약 체결 및 휴머노이드 로봇 관련 호재. 글로벌 대호재 2개 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '양자보안']</t>
+          <t>['AI 데이터센터', '로봇', '공급 계약']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8690</v>
+        <v>8735</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+5.98%</t>
+          <t>'+6.52%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.27</v>
       </c>
       <c r="E11" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H11" t="n">
         <v>1.42</v>
@@ -1438,7 +1438,7 @@
         <v>1.15</v>
       </c>
       <c r="O11" t="n">
-        <v>123069017150</v>
+        <v>124325757330</v>
       </c>
       <c r="P11" t="n">
         <v>9820</v>
@@ -1447,7 +1447,7 @@
         <v>2965</v>
       </c>
       <c r="R11" t="n">
-        <v>-67000</v>
+        <v>-57000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2575</v>
+        <v>2595</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+5.10%</t>
+          <t>'+5.92%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.68</v>
       </c>
       <c r="E12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H12" t="n">
         <v>1.69</v>
@@ -1530,7 +1530,7 @@
         <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>85297084682</v>
+        <v>85929026974</v>
       </c>
       <c r="P12" t="n">
         <v>2965</v>
@@ -1539,23 +1539,23 @@
         <v>865</v>
       </c>
       <c r="R12" t="n">
-        <v>-365000</v>
+        <v>-364000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>거래량 증가 및 개인 물량 흡수 기반 반등 기대. 전환사채 및 전환 이슈 존재.</t>
+          <t>거래량 증가 및 외국인 매수세 유입에 따른 상승 기대감. 2750원 돌파 시 추가 상승 전망. 전환사채 전환 이슈.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['거래량', '반등 기대', '전환사채']</t>
+          <t>['거래량', '외국인 매수', '전환사채']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64500</v>
+        <v>64200</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.70%</t>
+          <t>'+3.22%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>82</v>
       </c>
       <c r="G13" t="n">
-        <v>744</v>
+        <v>763</v>
       </c>
       <c r="H13" t="n">
         <v>41.01</v>
@@ -1622,7 +1622,7 @@
         <v>40.44</v>
       </c>
       <c r="O13" t="n">
-        <v>217195662500</v>
+        <v>219856972850</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1631,23 +1631,23 @@
         <v>23150</v>
       </c>
       <c r="R13" t="n">
-        <v>723000</v>
+        <v>773000</v>
       </c>
       <c r="S13" t="n">
-        <v>9000</v>
+        <v>-10000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 최근 코스피 수익률 1위 달성. 자사주 매입 진행 중이며, 10만원 목표 기대감 상승.</t>
+          <t>코스피 수익률 1위 달성 및 자사주 매입 지속, 공매도 세력에 대한 기대감으로 강한 상승세 전망. 귀족주 입성 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수익률', '자사주매입', '목표가']</t>
+          <t>['코스피 수익률', '자사주 매입', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>178500</v>
+        <v>8870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.41%</t>
+          <t>'+2.78%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.06</v>
+        <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>783</v>
+        <v>121</v>
       </c>
       <c r="F14" t="n">
-        <v>378</v>
+        <v>61</v>
       </c>
       <c r="G14" t="n">
-        <v>2692</v>
+        <v>206</v>
       </c>
       <c r="H14" t="n">
-        <v>35.43</v>
+        <v>5.47</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>174300</v>
+        <v>8630</v>
       </c>
       <c r="K14" t="n">
-        <v>181100</v>
+        <v>8660</v>
       </c>
       <c r="L14" t="n">
-        <v>186900</v>
+        <v>9190</v>
       </c>
       <c r="M14" t="n">
-        <v>178400</v>
+        <v>8410</v>
       </c>
       <c r="N14" t="n">
-        <v>35.49</v>
+        <v>5.34</v>
       </c>
       <c r="O14" t="n">
-        <v>151929950900</v>
+        <v>16478187955</v>
       </c>
       <c r="P14" t="n">
-        <v>304000</v>
+        <v>14940</v>
       </c>
       <c r="Q14" t="n">
-        <v>170900</v>
+        <v>5390</v>
       </c>
       <c r="R14" t="n">
-        <v>-30000</v>
+        <v>1000</v>
       </c>
       <c r="S14" t="n">
-        <v>5000</v>
+        <v>-1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>호재에도 불구하고 주가 하락. 프로그램 매수세 관찰, 외인/연기금 매도.</t>
+          <t>테슬라 로보택시 관련 상표 출원 뉴스에 따른 기대감 형성. 공매도 숏커버링 및 개인 물량 흡수 움직임 관찰. 주가 부진으로 인한 불만도 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['프로그램 매수', '공매 비율', '지수']</t>
+          <t>['테슬라', '로보택시', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>035420</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29975</v>
+        <v>178200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.61%</t>
+          <t>'+2.24%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>151</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>389</v>
       </c>
       <c r="G15" t="n">
-        <v>564</v>
+        <v>2661</v>
       </c>
       <c r="H15" t="n">
-        <v>28.81</v>
+        <v>35.43</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>29500</v>
+        <v>174300</v>
       </c>
       <c r="K15" t="n">
-        <v>29900</v>
+        <v>181100</v>
       </c>
       <c r="L15" t="n">
-        <v>30650</v>
+        <v>186900</v>
       </c>
       <c r="M15" t="n">
-        <v>29900</v>
+        <v>178000</v>
       </c>
       <c r="N15" t="n">
-        <v>28.82</v>
+        <v>35.49</v>
       </c>
       <c r="O15" t="n">
-        <v>31370363625</v>
+        <v>158692383000</v>
       </c>
       <c r="P15" t="n">
-        <v>69700</v>
+        <v>304000</v>
       </c>
       <c r="Q15" t="n">
-        <v>29200</v>
+        <v>170900</v>
       </c>
       <c r="R15" t="n">
-        <v>84000</v>
+        <v>-40000</v>
       </c>
       <c r="S15" t="n">
-        <v>4000</v>
+        <v>-11000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>카카오, 3만원 돌파 후에도 부정적 전망. 전환사채 및 스톡옵션 발행 조사 필요성 제기.</t>
+          <t>엔비디아 지분 투자 기대에도 불구하고 외국인, 연기금 매도 및 공매도 비율 증가로 인한 주가 부진 및 하락세 지속. 호재에도 오르지 못하는 상황에 대한 불만.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['전환사채', '스톡옵션', '부정적전망']</t>
+          <t>['엔비디아', '외국인 매도', '공매도 비율']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>035420</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16470</v>
+        <v>29950</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.49%</t>
+          <t>'+1.53%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G16" t="n">
-        <v>363</v>
+        <v>575</v>
       </c>
       <c r="H16" t="n">
-        <v>28.03</v>
+        <v>28.81</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>16390</v>
+        <v>29500</v>
       </c>
       <c r="K16" t="n">
-        <v>16630</v>
+        <v>29900</v>
       </c>
       <c r="L16" t="n">
-        <v>16760</v>
+        <v>30650</v>
       </c>
       <c r="M16" t="n">
-        <v>16300</v>
+        <v>29900</v>
       </c>
       <c r="N16" t="n">
-        <v>27.96</v>
+        <v>28.82</v>
       </c>
       <c r="O16" t="n">
-        <v>52527398035</v>
+        <v>32429289950</v>
       </c>
       <c r="P16" t="n">
-        <v>35350</v>
+        <v>69700</v>
       </c>
       <c r="Q16" t="n">
-        <v>16270</v>
+        <v>29200</v>
       </c>
       <c r="R16" t="n">
-        <v>-529000</v>
+        <v>69000</v>
       </c>
       <c r="S16" t="n">
-        <v>-73000</v>
+        <v>-12000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>삼성중공업, 주문량 대비 주가 하락에 대한 불만 제기. 실적 발표 후에도 주가 흐름 미미.</t>
+          <t>카카오, 3만원 돌파 후에도 부정적 전망. 전환사채 및 스톡옵션 발행 조사 필요성 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주문량', '실적발표', '주가하락']</t>
+          <t>['전환사채', '스톡옵션', '부정적전망']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>035720</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52400</v>
+        <v>16480</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.13%</t>
+          <t>'+0.55%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>474</v>
+        <v>147</v>
       </c>
       <c r="F17" t="n">
-        <v>267</v>
+        <v>95</v>
       </c>
       <c r="G17" t="n">
-        <v>1252</v>
+        <v>371</v>
       </c>
       <c r="H17" t="n">
-        <v>10.31</v>
+        <v>28.03</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>53000</v>
+        <v>16390</v>
       </c>
       <c r="K17" t="n">
-        <v>53400</v>
+        <v>16630</v>
       </c>
       <c r="L17" t="n">
-        <v>53800</v>
+        <v>16760</v>
       </c>
       <c r="M17" t="n">
-        <v>51200</v>
+        <v>16300</v>
       </c>
       <c r="N17" t="n">
-        <v>10.34</v>
+        <v>27.96</v>
       </c>
       <c r="O17" t="n">
-        <v>77489393800</v>
+        <v>53978141460</v>
       </c>
       <c r="P17" t="n">
-        <v>154800</v>
+        <v>35350</v>
       </c>
       <c r="Q17" t="n">
-        <v>51200</v>
+        <v>16270</v>
       </c>
       <c r="R17" t="n">
-        <v>-388000</v>
+        <v>-260000</v>
       </c>
       <c r="S17" t="n">
-        <v>-50000</v>
+        <v>-133000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 하락 및 2분기 실적 부진에 대한 실망감. 자사주 매입 및 증권가 전망 언급.</t>
+          <t>수주 증가에도 불구하고 주가 하락 및 실적 발표 후에도 의미 없는 움직임에 대한 불만 제기. 애널리스트 비판.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['실적', '자사주']</t>
+          <t>['수주', '실적 발표', '주가 하락']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>042660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14230</v>
+        <v>52500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.52%</t>
+          <t>'-0.94%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>264</v>
+        <v>485</v>
       </c>
       <c r="F18" t="n">
-        <v>118</v>
+        <v>268</v>
       </c>
       <c r="G18" t="n">
-        <v>606</v>
+        <v>1263</v>
       </c>
       <c r="H18" t="n">
-        <v>9.83</v>
+        <v>10.31</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>14450</v>
+        <v>53000</v>
       </c>
       <c r="K18" t="n">
-        <v>14750</v>
+        <v>53400</v>
       </c>
       <c r="L18" t="n">
-        <v>14870</v>
+        <v>53800</v>
       </c>
       <c r="M18" t="n">
-        <v>14090</v>
+        <v>51200</v>
       </c>
       <c r="N18" t="n">
-        <v>10.02</v>
+        <v>10.34</v>
       </c>
       <c r="O18" t="n">
-        <v>60996725455</v>
+        <v>79504547800</v>
       </c>
       <c r="P18" t="n">
-        <v>40350</v>
+        <v>154800</v>
       </c>
       <c r="Q18" t="n">
-        <v>3320</v>
+        <v>51200</v>
       </c>
       <c r="R18" t="n">
-        <v>-873000</v>
+        <v>-412000</v>
       </c>
       <c r="S18" t="n">
-        <v>-85000</v>
+        <v>-70000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>코스피 지수 대비 마이너스, 상폐 및 사기꾼 등 강한 부정적 감정 표출. 객관적 근거 부재.</t>
+          <t>주가 하락 및 2분기 실적 부진에 대한 실망감. 자사주 매입 및 증권가 전망 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['실적', '자사주']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>042660</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2015</v>
+        <v>14270</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.36%</t>
+          <t>'-1.25%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.39</v>
+        <v>-0.19</v>
       </c>
       <c r="E19" t="n">
-        <v>90</v>
+        <v>265</v>
       </c>
       <c r="F19" t="n">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="G19" t="n">
-        <v>119</v>
+        <v>608</v>
       </c>
       <c r="H19" t="n">
-        <v>2.52</v>
+        <v>9.83</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,130 +2159,130 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2085</v>
+        <v>14450</v>
       </c>
       <c r="K19" t="n">
-        <v>2005</v>
+        <v>14750</v>
       </c>
       <c r="L19" t="n">
-        <v>2025</v>
+        <v>14870</v>
       </c>
       <c r="M19" t="n">
-        <v>1805</v>
+        <v>14090</v>
       </c>
       <c r="N19" t="n">
-        <v>2.13</v>
+        <v>10.02</v>
       </c>
       <c r="O19" t="n">
-        <v>15499875971</v>
+        <v>61767022285</v>
       </c>
       <c r="P19" t="n">
-        <v>6190</v>
+        <v>40350</v>
       </c>
       <c r="Q19" t="n">
-        <v>636</v>
+        <v>3320</v>
       </c>
       <c r="R19" t="n">
-        <v>-1333000</v>
+        <v>-839000</v>
       </c>
       <c r="S19" t="n">
-        <v>19000</v>
+        <v>-141000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>SK하이닉스 연계 호재 언급 있으나, 액면병합 및 공매도 관련 부정적 논조.</t>
+          <t>주가 하락에 대한 불만과 경영진 비판. 상폐 및 부실 기업 의혹 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '공매도', '액면병합']</t>
+          <t>['상폐', '경영진']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>001510</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>SK증권</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2085</v>
+        <v>2035</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.92%</t>
+          <t>'-2.40%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.18</v>
+        <v>0.39</v>
       </c>
       <c r="E20" t="n">
         <v>90</v>
       </c>
       <c r="F20" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>323</v>
+        <v>121</v>
       </c>
       <c r="H20" t="n">
-        <v>5.07</v>
+        <v>2.52</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>2170</v>
+        <v>2085</v>
       </c>
       <c r="K20" t="n">
-        <v>2160</v>
+        <v>2005</v>
       </c>
       <c r="L20" t="n">
-        <v>2475</v>
+        <v>2035</v>
       </c>
       <c r="M20" t="n">
-        <v>2085</v>
+        <v>1805</v>
       </c>
       <c r="N20" t="n">
-        <v>4.89</v>
+        <v>2.13</v>
       </c>
       <c r="O20" t="n">
-        <v>50028268578</v>
+        <v>15746513411</v>
       </c>
       <c r="P20" t="n">
-        <v>4980</v>
+        <v>6190</v>
       </c>
       <c r="Q20" t="n">
-        <v>774</v>
+        <v>636</v>
       </c>
       <c r="R20" t="n">
-        <v>-105000</v>
+        <v>-1288000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세에도 불구하고 주가 흐름 둔화. 보호예수 해제 및 불확실성 존재.</t>
+          <t>SK하이닉스 연계 호재 언급 있으나, 액면병합 및 공매도 관련 부정적 논조.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['로봇 섹터', '보호예수', '주가 흐름']</t>
+          <t>['SK하이닉스', '공매도', '액면병합']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>001510</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9040</v>
+        <v>2095</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.14%</t>
+          <t>'-3.46%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.83</v>
+        <v>0.18</v>
       </c>
       <c r="E21" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F21" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G21" t="n">
-        <v>288</v>
+        <v>341</v>
       </c>
       <c r="H21" t="n">
-        <v>3.46</v>
+        <v>5.07</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>9530</v>
+        <v>2170</v>
       </c>
       <c r="K21" t="n">
-        <v>9560</v>
+        <v>2160</v>
       </c>
       <c r="L21" t="n">
-        <v>9850</v>
+        <v>2475</v>
       </c>
       <c r="M21" t="n">
-        <v>8870</v>
+        <v>2075</v>
       </c>
       <c r="N21" t="n">
-        <v>2.63</v>
+        <v>4.89</v>
       </c>
       <c r="O21" t="n">
-        <v>44411972320</v>
+        <v>50793242253</v>
       </c>
       <c r="P21" t="n">
-        <v>11690</v>
+        <v>4980</v>
       </c>
       <c r="Q21" t="n">
-        <v>2270</v>
+        <v>774</v>
       </c>
       <c r="R21" t="n">
-        <v>-5000</v>
+        <v>-83000</v>
       </c>
       <c r="S21" t="n">
-        <v>-71000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>하락 추세 및 8000원 목표가 전망. 매수 타이밍에 대한 부정적 의견.</t>
+          <t>로봇 섹터 강세에도 불구하고 주가 흐름 둔화. 보호예수 해제 및 불확실성 존재.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,18 +2383,110 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>['로봇 섹터', '보호예수', '주가 흐름']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>138360</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>9030</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>'-5.25%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E22" t="n">
+        <v>90</v>
+      </c>
+      <c r="F22" t="n">
+        <v>54</v>
+      </c>
+      <c r="G22" t="n">
+        <v>295</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>9530</v>
+      </c>
+      <c r="K22" t="n">
+        <v>9560</v>
+      </c>
+      <c r="L22" t="n">
+        <v>9850</v>
+      </c>
+      <c r="M22" t="n">
+        <v>8870</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O22" t="n">
+        <v>44804283340</v>
+      </c>
+      <c r="P22" t="n">
+        <v>11690</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-84000</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>하락 추세 및 8000원 목표가 전망. 매수 타이밍에 대한 부정적 의견.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>['하락 추세', '목표가', '매수 타이밍']</t>
         </is>
       </c>
-      <c r="X21" t="n">
+      <c r="X22" t="n">
         <v>1</v>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>추적</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>396300</t>
         </is>

--- a/data/trending_integrated_20261028_14.xlsx
+++ b/data/trending_integrated_20261028_14.xlsx
@@ -584,7 +584,7 @@
         <v>84</v>
       </c>
       <c r="G2" t="n">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>151204283371</v>
+        <v>151288250491</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27800</v>
+        <v>19160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.05%</t>
+          <t>'+21.04%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.15</v>
+        <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="G3" t="n">
-        <v>270</v>
+        <v>406</v>
       </c>
       <c r="H3" t="n">
-        <v>5.16</v>
+        <v>1.11</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,91 +687,91 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>23750</v>
+        <v>15830</v>
       </c>
       <c r="K3" t="n">
-        <v>24200</v>
+        <v>17170</v>
       </c>
       <c r="L3" t="n">
-        <v>29900</v>
+        <v>19800</v>
       </c>
       <c r="M3" t="n">
-        <v>24200</v>
+        <v>15830</v>
       </c>
       <c r="N3" t="n">
-        <v>5.31</v>
+        <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>172407391000</v>
+        <v>359194733660</v>
       </c>
       <c r="P3" t="n">
-        <v>50600</v>
+        <v>28800</v>
       </c>
       <c r="Q3" t="n">
-        <v>13210</v>
+        <v>11550</v>
       </c>
       <c r="R3" t="n">
-        <v>-27000</v>
+        <v>-87000</v>
       </c>
       <c r="S3" t="n">
-        <v>219000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>원익홀딩스, 로봇 관련주로 주목받으며 기대감 형성. 다만, 구체적인 호재보다는 기대감에 따른 변동성 언급.</t>
+          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 기대감. 반도체 업황 호조 속에서 3조 시가총액 달성 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇', '품절주', '인수']</t>
+          <t>['마이크론', 'ASML', '반도체 장비']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18410</v>
+        <v>27900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.30%</t>
+          <t>'+17.47%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.02</v>
+        <v>-0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="F4" t="n">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>398</v>
+        <v>273</v>
       </c>
       <c r="H4" t="n">
-        <v>1.11</v>
+        <v>5.16</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,60 +779,60 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15830</v>
+        <v>23750</v>
       </c>
       <c r="K4" t="n">
-        <v>17170</v>
+        <v>24200</v>
       </c>
       <c r="L4" t="n">
-        <v>19800</v>
+        <v>29900</v>
       </c>
       <c r="M4" t="n">
-        <v>15830</v>
+        <v>24200</v>
       </c>
       <c r="N4" t="n">
-        <v>0.09</v>
+        <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>346288826145</v>
+        <v>174630933875</v>
       </c>
       <c r="P4" t="n">
-        <v>28800</v>
+        <v>50600</v>
       </c>
       <c r="Q4" t="n">
-        <v>11550</v>
+        <v>13210</v>
       </c>
       <c r="R4" t="n">
-        <v>-87000</v>
+        <v>-27000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>219000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스, 삼성전자·하이닉스·마이크론 등 빅테크 협력사 관련 긍정적 전망. 4분기 공급 가시화.</t>
+          <t>원익홀딩스, 로봇 관련주로 주목받으며 기대감 형성. 다만, 구체적인 호재보다는 기대감에 따른 변동성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['마이크론', 'ASML', '반도체 장비']</t>
+          <t>['로봇', '품절주', '인수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>190350</v>
+        <v>190600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.25%</t>
+          <t>'+11.40%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" t="n">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="H5" t="n">
         <v>74.90000000000001</v>
@@ -886,7 +886,7 @@
         <v>74.89</v>
       </c>
       <c r="O5" t="n">
-        <v>691847062250</v>
+        <v>707906325950</v>
       </c>
       <c r="P5" t="n">
         <v>243500</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1486000</v>
+        <v>1485000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.81%</t>
+          <t>'+10.74%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="G6" t="n">
-        <v>1813</v>
+        <v>1904</v>
       </c>
       <c r="H6" t="n">
         <v>48.61</v>
@@ -969,7 +969,7 @@
         <v>1390000</v>
       </c>
       <c r="L6" t="n">
-        <v>1488000</v>
+        <v>1492000</v>
       </c>
       <c r="M6" t="n">
         <v>1358000</v>
@@ -978,7 +978,7 @@
         <v>48.66</v>
       </c>
       <c r="O6" t="n">
-        <v>4495463249500</v>
+        <v>4626353841500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>4분기 실적 100조 예상 및 반도체 2차 랠리 시작 기대감으로 강한 상승세 전망. 개인 매도세 관찰.</t>
+          <t>TSMC 대비 저평가 및 외국인 매수세 유입에 따른 반도체 2차 랠리 시작 기대감. 4분기 실적 발표 후에도 상승세를 이어갈 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['4분기 실적', '반도체 랠리', '개인 매도']</t>
+          <t>['반도체 2차 랠리', '외국인 매수', '실적 발표']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15040</v>
+        <v>15000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.78%</t>
+          <t>'+9.49%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F7" t="n">
         <v>78</v>
       </c>
       <c r="G7" t="n">
-        <v>642</v>
+        <v>689</v>
       </c>
       <c r="H7" t="n">
         <v>2.87</v>
@@ -1070,7 +1070,7 @@
         <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>168596287900</v>
+        <v>170607152695</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>국민연금 매수 및 외국인 프로그램 매수세 집중, 미래 기술 Seed 전략 수립 관련 기대감으로 강한 상승세 전망. 공매도 압박.</t>
+          <t>메타 유리기판 및 해상광통신 케이블 관련 사업 기대감. 외국인 프로그램 매수세 유입 및 공매도 세력과의 대결 구도로 인한 2만원 돌파 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['국민연금', '외국인 프로그램', '미래 기술']</t>
+          <t>['유리기판', '해상광통신', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>242250</v>
+        <v>242000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.12%</t>
+          <t>'+9.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="G8" t="n">
-        <v>1639</v>
+        <v>1630</v>
       </c>
       <c r="H8" t="n">
         <v>46.15</v>
@@ -1162,7 +1162,7 @@
         <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3056771873250</v>
+        <v>3144715428250</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>노무라 증권 목표가 하향에도 불구하고, 3분기 예상 순이익 전망 및 자사주 소각 기대감으로 단기 상승 기대. 단, 감정적 표현 다수.</t>
+          <t>노무라 증권 목표가 하향 조정 및 삼성전자 성과급 논란 속, 3분기 순이익 115조 예상 및 자사주 소각/특별배당 공시 기대감으로 인한 상승 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['노무라 증권', '자사주 소각', '실적 전망']</t>
+          <t>['성과급', '자사주 소각', '특별배당']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19400</v>
+        <v>19330</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.44%</t>
+          <t>'+8.05%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,7 +1225,7 @@
         <v>92</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
         <v>112</v>
@@ -1254,7 +1254,7 @@
         <v>3.79</v>
       </c>
       <c r="O9" t="n">
-        <v>70145984045</v>
+        <v>70820292475</v>
       </c>
       <c r="P9" t="n">
         <v>22450</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18380</v>
+        <v>18360</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.55%</t>
+          <t>'+7.43%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.61</v>
       </c>
       <c r="E10" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F10" t="n">
         <v>75</v>
       </c>
       <c r="G10" t="n">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="H10" t="n">
         <v>4.74</v>
@@ -1346,7 +1346,7 @@
         <v>4.13</v>
       </c>
       <c r="O10" t="n">
-        <v>46136697450</v>
+        <v>46357871310</v>
       </c>
       <c r="P10" t="n">
         <v>28600</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>AI 데이터센터 방열 시스템 공급 계약 체결 및 휴머노이드 로봇 관련 호재. 글로벌 대호재 2개 존재.</t>
+          <t>아틀라스 발주, 로봇 눈 공개, AI 데이터센터 방열 시스템 공급 계약 등 다수의 호재를 기반으로 한 강한 상승 기대감. 휴머노이드 로봇 산업 성장과 연계.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '로봇', '공급 계약']</t>
+          <t>['로봇', 'AI', '휴머노이드']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8735</v>
+        <v>2600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+6.52%</t>
+          <t>'+6.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.27</v>
+        <v>0.68</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="F11" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G11" t="n">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="H11" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8200</v>
+        <v>2450</v>
       </c>
       <c r="K11" t="n">
-        <v>8230</v>
+        <v>2525</v>
       </c>
       <c r="L11" t="n">
-        <v>9780</v>
+        <v>2965</v>
       </c>
       <c r="M11" t="n">
-        <v>8100</v>
+        <v>2505</v>
       </c>
       <c r="N11" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>124325757330</v>
+        <v>86359144947</v>
       </c>
       <c r="P11" t="n">
-        <v>9820</v>
+        <v>2965</v>
       </c>
       <c r="Q11" t="n">
-        <v>2965</v>
+        <v>865</v>
       </c>
       <c r="R11" t="n">
-        <v>-57000</v>
+        <v>-364000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 양자/보안주 급등 및 국내 해킹 사고 관련, 보안 테마 상승 기대.</t>
+          <t>거래량 증가 및 외국인 순매수세에 힘입어 2600원대 저항선 돌파 시도. 개인 물량 흡수 후 시세 분출 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '테마']</t>
+          <t>['외국인 순매수', '거래량', '시세 분출']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,43 +1471,43 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2595</v>
+        <v>8640</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+5.92%</t>
+          <t>'+5.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.68</v>
+        <v>0.27</v>
       </c>
       <c r="E12" t="n">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="F12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G12" t="n">
-        <v>152</v>
+        <v>98</v>
       </c>
       <c r="H12" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2450</v>
+        <v>8200</v>
       </c>
       <c r="K12" t="n">
-        <v>2525</v>
+        <v>8230</v>
       </c>
       <c r="L12" t="n">
+        <v>9780</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8100</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O12" t="n">
+        <v>124979840030</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9820</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2965</v>
       </c>
-      <c r="M12" t="n">
-        <v>2505</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O12" t="n">
-        <v>85929026974</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2965</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>865</v>
-      </c>
       <c r="R12" t="n">
-        <v>-364000</v>
+        <v>-57000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>거래량 증가 및 외국인 매수세 유입에 따른 상승 기대감. 2750원 돌파 시 추가 상승 전망. 전환사채 전환 이슈.</t>
+          <t>미국 양자/보안주 급등 및 국내 해킹 사고 관련, 보안 테마 상승 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['거래량', '외국인 매수', '전환사채']</t>
+          <t>['보안', '해킹', '테마']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,43 +1563,43 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64200</v>
+        <v>8910</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.22%</t>
+          <t>'+3.24%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.57</v>
+        <v>0.13</v>
       </c>
       <c r="E13" t="n">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="F13" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="G13" t="n">
-        <v>763</v>
+        <v>233</v>
       </c>
       <c r="H13" t="n">
-        <v>41.01</v>
+        <v>5.47</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>62200</v>
+        <v>8630</v>
       </c>
       <c r="K13" t="n">
-        <v>63000</v>
+        <v>8660</v>
       </c>
       <c r="L13" t="n">
-        <v>64900</v>
+        <v>9190</v>
       </c>
       <c r="M13" t="n">
-        <v>62200</v>
+        <v>8410</v>
       </c>
       <c r="N13" t="n">
-        <v>40.44</v>
+        <v>5.34</v>
       </c>
       <c r="O13" t="n">
-        <v>219856972850</v>
+        <v>17425630385</v>
       </c>
       <c r="P13" t="n">
-        <v>67300</v>
+        <v>14940</v>
       </c>
       <c r="Q13" t="n">
-        <v>23150</v>
+        <v>5390</v>
       </c>
       <c r="R13" t="n">
-        <v>773000</v>
+        <v>1000</v>
       </c>
       <c r="S13" t="n">
-        <v>-10000</v>
+        <v>-1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>코스피 수익률 1위 달성 및 자사주 매입 지속, 공매도 세력에 대한 기대감으로 강한 상승세 전망. 귀족주 입성 기대.</t>
+          <t>테슬라 로보택시 상표 출원 뉴스에도 불구하고 주가 부진. 공매도 세력과의 팽팽한 대결 속에서 개인 투자자들의 어려움 가중.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['코스피 수익률', '자사주 매입', '공매도']</t>
+          <t>['로보택시', '공매도', '테슬라']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8870</v>
+        <v>64200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.78%</t>
+          <t>'+3.22%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.13</v>
+        <v>0.57</v>
       </c>
       <c r="E14" t="n">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="F14" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="G14" t="n">
-        <v>206</v>
+        <v>778</v>
       </c>
       <c r="H14" t="n">
-        <v>5.47</v>
+        <v>41.01</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8630</v>
+        <v>62200</v>
       </c>
       <c r="K14" t="n">
-        <v>8660</v>
+        <v>63000</v>
       </c>
       <c r="L14" t="n">
-        <v>9190</v>
+        <v>64900</v>
       </c>
       <c r="M14" t="n">
-        <v>8410</v>
+        <v>62200</v>
       </c>
       <c r="N14" t="n">
-        <v>5.34</v>
+        <v>40.44</v>
       </c>
       <c r="O14" t="n">
-        <v>16478187955</v>
+        <v>224292756750</v>
       </c>
       <c r="P14" t="n">
-        <v>14940</v>
+        <v>67300</v>
       </c>
       <c r="Q14" t="n">
-        <v>5390</v>
+        <v>23150</v>
       </c>
       <c r="R14" t="n">
-        <v>1000</v>
+        <v>773000</v>
       </c>
       <c r="S14" t="n">
-        <v>-1000</v>
+        <v>-10000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>테슬라 로보택시 관련 상표 출원 뉴스에 따른 기대감 형성. 공매도 숏커버링 및 개인 물량 흡수 움직임 관찰. 주가 부진으로 인한 불만도 존재.</t>
+          <t>이란 최고지도자 발언 이후 전쟁 종식 기대감 속, 최근 4일간 코스피 수익률 1위 달성. 자사주 매입 및 공매도 세력과의 대결 구도로 인한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['테슬라', '로보택시', '공매도']</t>
+          <t>['자사주 매입', '공매도', '이란 최고지도자']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>178200</v>
+        <v>178700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.24%</t>
+          <t>'+2.52%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1780,7 +1780,7 @@
         <v>389</v>
       </c>
       <c r="G15" t="n">
-        <v>2661</v>
+        <v>2603</v>
       </c>
       <c r="H15" t="n">
         <v>35.43</v>
@@ -1806,7 +1806,7 @@
         <v>35.49</v>
       </c>
       <c r="O15" t="n">
-        <v>158692383000</v>
+        <v>165390733650</v>
       </c>
       <c r="P15" t="n">
         <v>304000</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>엔비디아 지분 투자 기대에도 불구하고 외국인, 연기금 매도 및 공매도 비율 증가로 인한 주가 부진 및 하락세 지속. 호재에도 오르지 못하는 상황에 대한 불만.</t>
+          <t>엔비디아 지분 투자 및 브룩필드 관련 호재에도 불구하고 주가 하락. 외국인, 연기금 매도 및 공매도 비율 증가로 인한 부정적 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['엔비디아', '외국인 매도', '공매도 비율']</t>
+          <t>['엔비디아', '공매도', '외국인 매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29950</v>
+        <v>30050</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.53%</t>
+          <t>'+1.86%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F16" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G16" t="n">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="H16" t="n">
         <v>28.81</v>
@@ -1898,7 +1898,7 @@
         <v>28.82</v>
       </c>
       <c r="O16" t="n">
-        <v>32429289950</v>
+        <v>33604663325</v>
       </c>
       <c r="P16" t="n">
         <v>69700</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>카카오, 3만원 돌파 후에도 부정적 전망. 전환사채 및 스톡옵션 발행 조사 필요성 제기.</t>
+          <t>전환사채 발행 관련 불투명성과 공매도 관련 부정적 전망 속에서 거래량 부진 시 추가 하락 예상. 일부 투자자에게는 긍정적 가격 움직임 나타남.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['전환사채', '스톡옵션', '부정적전망']</t>
+          <t>['전환사채', '공매도', '거래량']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16480</v>
+        <v>16510</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.55%</t>
+          <t>'+0.73%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F17" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G17" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H17" t="n">
         <v>28.03</v>
@@ -1990,7 +1990,7 @@
         <v>27.96</v>
       </c>
       <c r="O17" t="n">
-        <v>53978141460</v>
+        <v>56018418910</v>
       </c>
       <c r="P17" t="n">
         <v>35350</v>
@@ -2050,13 +2050,13 @@
         <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="F18" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G18" t="n">
-        <v>1263</v>
+        <v>1291</v>
       </c>
       <c r="H18" t="n">
         <v>10.31</v>
@@ -2082,7 +2082,7 @@
         <v>10.34</v>
       </c>
       <c r="O18" t="n">
-        <v>79504547800</v>
+        <v>80880099300</v>
       </c>
       <c r="P18" t="n">
         <v>154800</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 하락 및 2분기 실적 부진에 대한 실망감. 자사주 매입 및 증권가 전망 언급.</t>
+          <t>코스피 대세 상승 및 미국 정상회담 기대감에도 불구하고 주가 하락. 조선업 협력 난항 및 과거 실적 부진으로 인한 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적', '자사주']</t>
+          <t>['조선업', '실적 부진', '투자 심리']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14270</v>
+        <v>14290</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-1.25%</t>
+          <t>'-1.11%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.19</v>
       </c>
       <c r="E19" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F19" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G19" t="n">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="H19" t="n">
         <v>9.83</v>
@@ -2174,7 +2174,7 @@
         <v>10.02</v>
       </c>
       <c r="O19" t="n">
-        <v>61767022285</v>
+        <v>63304565105</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 불만과 경영진 비판. 상폐 및 부실 기업 의혹 제기.</t>
+          <t>코스피 지수 상승에도 불구하고 하락하며 투자자들의 불만 고조. 경영진의 보여주기식 행보 부재 및 원전 사업 불확실성으로 인한 부정적 전망.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['상폐', '경영진']</t>
+          <t>['경영진', '원전 사업', '주주 불만']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>0.39</v>
       </c>
       <c r="E20" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F20" t="n">
         <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H20" t="n">
         <v>2.52</v>
@@ -2257,7 +2257,7 @@
         <v>2005</v>
       </c>
       <c r="L20" t="n">
-        <v>2035</v>
+        <v>2055</v>
       </c>
       <c r="M20" t="n">
         <v>1805</v>
@@ -2266,7 +2266,7 @@
         <v>2.13</v>
       </c>
       <c r="O20" t="n">
-        <v>15746513411</v>
+        <v>16168349076</v>
       </c>
       <c r="P20" t="n">
         <v>6190</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2095</v>
+        <v>2070</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-3.46%</t>
+          <t>'-4.61%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.18</v>
       </c>
       <c r="E21" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F21" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="H21" t="n">
         <v>5.07</v>
@@ -2352,13 +2352,13 @@
         <v>2475</v>
       </c>
       <c r="M21" t="n">
-        <v>2075</v>
+        <v>2060</v>
       </c>
       <c r="N21" t="n">
         <v>4.89</v>
       </c>
       <c r="O21" t="n">
-        <v>50793242253</v>
+        <v>51357506275</v>
       </c>
       <c r="P21" t="n">
         <v>4980</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9030</v>
+        <v>9010</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-5.25%</t>
+          <t>'-5.46%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.83</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F22" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G22" t="n">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="H22" t="n">
         <v>3.46</v>
@@ -2450,7 +2450,7 @@
         <v>2.63</v>
       </c>
       <c r="O22" t="n">
-        <v>44804283340</v>
+        <v>45295114385</v>
       </c>
       <c r="P22" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261028_14.xlsx
+++ b/data/trending_integrated_20261028_14.xlsx
@@ -584,7 +584,7 @@
         <v>84</v>
       </c>
       <c r="G2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>151288250491</v>
+        <v>151353734441</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19160</v>
+        <v>19280</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.04%</t>
+          <t>'+21.79%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="F3" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G3" t="n">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="H3" t="n">
         <v>1.11</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>359194733660</v>
+        <v>370895373310</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27900</v>
+        <v>28050</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.47%</t>
+          <t>'+18.11%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H4" t="n">
         <v>5.16</v>
@@ -794,7 +794,7 @@
         <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>174630933875</v>
+        <v>175505073900</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>190600</v>
+        <v>190100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.40%</t>
+          <t>'+11.10%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>71</v>
       </c>
       <c r="G5" t="n">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="H5" t="n">
         <v>74.90000000000001</v>
@@ -886,7 +886,7 @@
         <v>74.89</v>
       </c>
       <c r="O5" t="n">
-        <v>707906325950</v>
+        <v>719338210400</v>
       </c>
       <c r="P5" t="n">
         <v>243500</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1485000</v>
+        <v>1484000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.74%</t>
+          <t>'+10.66%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="G6" t="n">
-        <v>1904</v>
+        <v>1834</v>
       </c>
       <c r="H6" t="n">
         <v>48.61</v>
@@ -978,7 +978,7 @@
         <v>48.66</v>
       </c>
       <c r="O6" t="n">
-        <v>4626353841500</v>
+        <v>4715289626500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>TSMC 대비 저평가 및 외국인 매수세 유입에 따른 반도체 2차 랠리 시작 기대감. 4분기 실적 발표 후에도 상승세를 이어갈 전망.</t>
+          <t>반도체 2차 랠리 및 연말 목표가 제시 등 긍정적 전망 다수. 실적 발표 후에도 주가 상승 기대감을 보이나, 구체적인 근거는 부족.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체 2차 랠리', '외국인 매수', '실적 발표']</t>
+          <t>['반도체', '실적발표', '목표가']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15000</v>
+        <v>14950</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.49%</t>
+          <t>'+9.12%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G7" t="n">
-        <v>689</v>
+        <v>709</v>
       </c>
       <c r="H7" t="n">
         <v>2.87</v>
@@ -1070,7 +1070,7 @@
         <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>170607152695</v>
+        <v>171779051510</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>메타 유리기판 및 해상광통신 케이블 관련 사업 기대감. 외국인 프로그램 매수세 유입 및 공매도 세력과의 대결 구도로 인한 2만원 돌파 전망.</t>
+          <t>미래 기술(메타 유리기판, 해상광통신) 및 AI 수요 관련 뉴스와 외국인 프로그램 매수를 근거로 긍정적 전망. 공매도 세력에 대한 경계 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유리기판', '해상광통신', '공매도']</t>
+          <t>['AI', '유리기판', '외국인']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>242000</v>
+        <v>241500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.01%</t>
+          <t>'+8.78%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="G8" t="n">
-        <v>1630</v>
+        <v>1619</v>
       </c>
       <c r="H8" t="n">
         <v>46.15</v>
@@ -1162,7 +1162,7 @@
         <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3144715428250</v>
+        <v>3219819146250</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>노무라 증권 목표가 하향 조정 및 삼성전자 성과급 논란 속, 3분기 순이익 115조 예상 및 자사주 소각/특별배당 공시 기대감으로 인한 상승 전망.</t>
+          <t>노무라 증권 목표가 하향에도 불구하고, 3분기 순이익 예상치 및 자사주 소각 기대감 언급. 다만, 객관적 근거 부족으로 fact_score는 보수적으로 평가.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['성과급', '자사주 소각', '특별배당']</t>
+          <t>['자사주소각', '실적발표', '목표가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19330</v>
+        <v>18490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.05%</t>
+          <t>'+8.19%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="E9" t="n">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="G9" t="n">
-        <v>112</v>
+        <v>412</v>
       </c>
       <c r="H9" t="n">
-        <v>4.25</v>
+        <v>4.74</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17890</v>
+        <v>17090</v>
       </c>
       <c r="K9" t="n">
-        <v>18250</v>
+        <v>19270</v>
       </c>
       <c r="L9" t="n">
-        <v>20000</v>
+        <v>20450</v>
       </c>
       <c r="M9" t="n">
-        <v>17950</v>
+        <v>18070</v>
       </c>
       <c r="N9" t="n">
-        <v>3.79</v>
+        <v>4.13</v>
       </c>
       <c r="O9" t="n">
-        <v>70820292475</v>
+        <v>46527923315</v>
       </c>
       <c r="P9" t="n">
-        <v>22450</v>
+        <v>28600</v>
       </c>
       <c r="Q9" t="n">
-        <v>6320</v>
+        <v>11050</v>
       </c>
       <c r="R9" t="n">
-        <v>-7000</v>
+        <v>-59000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국내외 해킹 사고 연이은 발생, 양자보안 의무화 등 보안 섹터 상승 기대.</t>
+          <t>아틀라스 발주, 로봇 눈 공개, AI 데이터센터 방열 시스템 공급 계약 등 다수의 호재를 기반으로 한 강한 상승 기대감. 휴머노이드 로봇 산업 성장과 연계.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '양자보안']</t>
+          <t>['로봇', 'AI', '휴머노이드']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18360</v>
+        <v>19260</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.43%</t>
+          <t>'+7.66%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="F10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>408</v>
+        <v>112</v>
       </c>
       <c r="H10" t="n">
-        <v>4.74</v>
+        <v>4.25</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17090</v>
+        <v>17890</v>
       </c>
       <c r="K10" t="n">
-        <v>19270</v>
+        <v>18250</v>
       </c>
       <c r="L10" t="n">
-        <v>20450</v>
+        <v>20000</v>
       </c>
       <c r="M10" t="n">
-        <v>18070</v>
+        <v>17950</v>
       </c>
       <c r="N10" t="n">
-        <v>4.13</v>
+        <v>3.79</v>
       </c>
       <c r="O10" t="n">
-        <v>46357871310</v>
+        <v>71118719595</v>
       </c>
       <c r="P10" t="n">
-        <v>28600</v>
+        <v>22450</v>
       </c>
       <c r="Q10" t="n">
-        <v>11050</v>
+        <v>6320</v>
       </c>
       <c r="R10" t="n">
-        <v>-59000</v>
+        <v>-7000</v>
       </c>
       <c r="S10" t="n">
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>아틀라스 발주, 로봇 눈 공개, AI 데이터센터 방열 시스템 공급 계약 등 다수의 호재를 기반으로 한 강한 상승 기대감. 휴머노이드 로봇 산업 성장과 연계.</t>
+          <t>국내외 해킹 사고 연이은 발생, 양자보안 의무화 등 보안 섹터 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['로봇', 'AI', '휴머노이드']</t>
+          <t>['보안', '해킹', '양자보안']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2600</v>
+        <v>2615</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+6.12%</t>
+          <t>'+6.73%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.68</v>
       </c>
       <c r="E11" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F11" t="n">
         <v>67</v>
       </c>
       <c r="G11" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="H11" t="n">
         <v>1.69</v>
@@ -1438,7 +1438,7 @@
         <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>86359144947</v>
+        <v>87073405982</v>
       </c>
       <c r="P11" t="n">
         <v>2965</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>거래량 증가 및 외국인 순매수세에 힘입어 2600원대 저항선 돌파 시도. 개인 물량 흡수 후 시세 분출 기대감.</t>
+          <t>거래량 증가 및 외국인 매수세 유입을 근거로 긍정적 전망 제시. 개인 물량 흡수 및 시세 분출 기대감 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['외국인 순매수', '거래량', '시세 분출']</t>
+          <t>['거래량', '외국인', '손바뀜']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,79 +1483,79 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8640</v>
+        <v>9170</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+5.37%</t>
+          <t>'+6.26%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="E12" t="n">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="F12" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G12" t="n">
-        <v>98</v>
+        <v>259</v>
       </c>
       <c r="H12" t="n">
-        <v>1.42</v>
+        <v>5.47</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8200</v>
+        <v>8630</v>
       </c>
       <c r="K12" t="n">
-        <v>8230</v>
+        <v>8660</v>
       </c>
       <c r="L12" t="n">
-        <v>9780</v>
+        <v>9190</v>
       </c>
       <c r="M12" t="n">
-        <v>8100</v>
+        <v>8410</v>
       </c>
       <c r="N12" t="n">
-        <v>1.15</v>
+        <v>5.34</v>
       </c>
       <c r="O12" t="n">
-        <v>124979840030</v>
+        <v>19609399785</v>
       </c>
       <c r="P12" t="n">
-        <v>9820</v>
+        <v>14940</v>
       </c>
       <c r="Q12" t="n">
-        <v>2965</v>
+        <v>5390</v>
       </c>
       <c r="R12" t="n">
-        <v>-57000</v>
+        <v>1000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 양자/보안주 급등 및 국내 해킹 사고 관련, 보안 테마 상승 기대.</t>
+          <t>테슬라 로보택시 관련 뉴스 언급에도 불구하고, 낮은 주가 상승률 및 공매도 관련 부정적 의견이 많음. 주가 상승 동력 부족.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '테마']</t>
+          <t>['공매도', '로보택시', '주가']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,91 +1563,91 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8910</v>
+        <v>8670</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.24%</t>
+          <t>'+5.73%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.13</v>
+        <v>0.27</v>
       </c>
       <c r="E13" t="n">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="F13" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G13" t="n">
-        <v>233</v>
+        <v>99</v>
       </c>
       <c r="H13" t="n">
-        <v>5.47</v>
+        <v>1.42</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8630</v>
+        <v>8200</v>
       </c>
       <c r="K13" t="n">
-        <v>8660</v>
+        <v>8230</v>
       </c>
       <c r="L13" t="n">
-        <v>9190</v>
+        <v>9780</v>
       </c>
       <c r="M13" t="n">
-        <v>8410</v>
+        <v>8100</v>
       </c>
       <c r="N13" t="n">
-        <v>5.34</v>
+        <v>1.15</v>
       </c>
       <c r="O13" t="n">
-        <v>17425630385</v>
+        <v>125291043155</v>
       </c>
       <c r="P13" t="n">
-        <v>14940</v>
+        <v>9820</v>
       </c>
       <c r="Q13" t="n">
-        <v>5390</v>
+        <v>2965</v>
       </c>
       <c r="R13" t="n">
-        <v>1000</v>
+        <v>-57000</v>
       </c>
       <c r="S13" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>테슬라 로보택시 상표 출원 뉴스에도 불구하고 주가 부진. 공매도 세력과의 팽팽한 대결 속에서 개인 투자자들의 어려움 가중.</t>
+          <t>미국 양자/보안주 급등 및 국내 해킹 사고 관련, 보안 테마 상승 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['로보택시', '공매도', '테슬라']</t>
+          <t>['보안', '해킹', '테마']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>64200</v>
+        <v>64000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.22%</t>
+          <t>'+2.89%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.57</v>
       </c>
       <c r="E14" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F14" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G14" t="n">
-        <v>778</v>
+        <v>800</v>
       </c>
       <c r="H14" t="n">
         <v>41.01</v>
@@ -1714,7 +1714,7 @@
         <v>40.44</v>
       </c>
       <c r="O14" t="n">
-        <v>224292756750</v>
+        <v>227695405200</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>178700</v>
+        <v>178250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.52%</t>
+          <t>'+2.27%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G15" t="n">
-        <v>2603</v>
+        <v>2544</v>
       </c>
       <c r="H15" t="n">
         <v>35.43</v>
@@ -1806,7 +1806,7 @@
         <v>35.49</v>
       </c>
       <c r="O15" t="n">
-        <v>165390733650</v>
+        <v>168883191650</v>
       </c>
       <c r="P15" t="n">
         <v>304000</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>엔비디아 지분 투자 및 브룩필드 관련 호재에도 불구하고 주가 하락. 외국인, 연기금 매도 및 공매도 비율 증가로 인한 부정적 전망.</t>
+          <t>엔비디아 지분 투자 및 글로벌 전기차 부품 공급 관련 언급에도 불구하고, 주가 부진에 대한 불만 표출. 외국인 및 연기금 매도세 지적.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['엔비디아', '공매도', '외국인 매도']</t>
+          <t>['지분투자', '주가부진', '매도세']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30050</v>
+        <v>30000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.86%</t>
+          <t>'+1.69%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F16" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G16" t="n">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="H16" t="n">
         <v>28.81</v>
@@ -1898,7 +1898,7 @@
         <v>28.82</v>
       </c>
       <c r="O16" t="n">
-        <v>33604663325</v>
+        <v>34034339400</v>
       </c>
       <c r="P16" t="n">
         <v>69700</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16510</v>
+        <v>16500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.73%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F17" t="n">
         <v>94</v>
       </c>
       <c r="G17" t="n">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="H17" t="n">
         <v>28.03</v>
@@ -1990,7 +1990,7 @@
         <v>27.96</v>
       </c>
       <c r="O17" t="n">
-        <v>56018418910</v>
+        <v>57264675820</v>
       </c>
       <c r="P17" t="n">
         <v>35350</v>
@@ -2050,13 +2050,13 @@
         <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F18" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G18" t="n">
-        <v>1291</v>
+        <v>1313</v>
       </c>
       <c r="H18" t="n">
         <v>10.31</v>
@@ -2082,7 +2082,7 @@
         <v>10.34</v>
       </c>
       <c r="O18" t="n">
-        <v>80880099300</v>
+        <v>81649195900</v>
       </c>
       <c r="P18" t="n">
         <v>154800</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14290</v>
+        <v>14280</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-1.11%</t>
+          <t>'-1.18%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.19</v>
       </c>
       <c r="E19" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F19" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G19" t="n">
-        <v>624</v>
+        <v>653</v>
       </c>
       <c r="H19" t="n">
         <v>9.83</v>
@@ -2174,7 +2174,7 @@
         <v>10.02</v>
       </c>
       <c r="O19" t="n">
-        <v>63304565105</v>
+        <v>64317724835</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>코스피 지수 상승에도 불구하고 하락하며 투자자들의 불만 고조. 경영진의 보여주기식 행보 부재 및 원전 사업 불확실성으로 인한 부정적 전망.</t>
+          <t>코스피 상승장 속 하락하며 상폐 및 경영진 비판 등 부정적 의견 다수. 영업이익 증가에도 주가 하락에 대한 의문 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['경영진', '원전 사업', '주주 불만']</t>
+          <t>['상폐', '경영진', '영업이익']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.40%</t>
+          <t>'-2.16%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H20" t="n">
         <v>2.52</v>
@@ -2266,7 +2266,7 @@
         <v>2.13</v>
       </c>
       <c r="O20" t="n">
-        <v>16168349076</v>
+        <v>16273051571</v>
       </c>
       <c r="P20" t="n">
         <v>6190</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2070</v>
+        <v>2080</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-4.61%</t>
+          <t>'-4.15%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.18</v>
       </c>
       <c r="E21" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G21" t="n">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="H21" t="n">
         <v>5.07</v>
@@ -2358,7 +2358,7 @@
         <v>4.89</v>
       </c>
       <c r="O21" t="n">
-        <v>51357506275</v>
+        <v>51680627055</v>
       </c>
       <c r="P21" t="n">
         <v>4980</v>
@@ -2450,7 +2450,7 @@
         <v>2.63</v>
       </c>
       <c r="O22" t="n">
-        <v>45295114385</v>
+        <v>45600415155</v>
       </c>
       <c r="P22" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261028_14.xlsx
+++ b/data/trending_integrated_20261028_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G2" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>151353734441</v>
+        <v>151390205771</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>빛과전자, 상한가 기록 후 연상 기대감. 과거 쓰레기 회사에서 벗어나 긍정적 주가 흐름 전망.</t>
+          <t>미국 광통신주 상승에 따른 기대감. 상한가 기록 및 연상 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['상한가', '연상', '주가흐름']</t>
+          <t>['광통신', '상한가', '연상']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,7 +643,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19280</v>
+        <v>19770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.79%</t>
+          <t>'+24.89%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="F3" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G3" t="n">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="H3" t="n">
         <v>1.11</v>
@@ -693,7 +693,7 @@
         <v>17170</v>
       </c>
       <c r="L3" t="n">
-        <v>19800</v>
+        <v>19850</v>
       </c>
       <c r="M3" t="n">
         <v>15830</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>370895373310</v>
+        <v>382440231060</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 기대감. 반도체 업황 호조 속에서 3조 시가총액 달성 가능성 언급.</t>
+          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스. 글로벌 반도체 시장에서의 입지 강화 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['마이크론', 'ASML', '반도체 장비']</t>
+          <t>['반도체 장비', 'ASML', '공급망']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28050</v>
+        <v>27900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+18.11%</t>
+          <t>'+17.47%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H4" t="n">
         <v>5.16</v>
@@ -794,7 +794,7 @@
         <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>175505073900</v>
+        <v>176358280975</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>190100</v>
+        <v>189900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.10%</t>
+          <t>'+10.99%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>71</v>
       </c>
       <c r="G5" t="n">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="H5" t="n">
         <v>74.90000000000001</v>
@@ -886,7 +886,7 @@
         <v>74.89</v>
       </c>
       <c r="O5" t="n">
-        <v>719338210400</v>
+        <v>734890559900</v>
       </c>
       <c r="P5" t="n">
         <v>243500</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1484000</v>
+        <v>1481000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.66%</t>
+          <t>'+10.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G6" t="n">
-        <v>1834</v>
+        <v>1900</v>
       </c>
       <c r="H6" t="n">
         <v>48.61</v>
@@ -978,7 +978,7 @@
         <v>48.66</v>
       </c>
       <c r="O6" t="n">
-        <v>4715289626500</v>
+        <v>4808626417500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>반도체 2차 랠리 및 연말 목표가 제시 등 긍정적 전망 다수. 실적 발표 후에도 주가 상승 기대감을 보이나, 구체적인 근거는 부족.</t>
+          <t>실적 발표 후에도 상승 기대감. 외국인 매수세 유입 가능성과 연말 목표 주가 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체', '실적발표', '목표가']</t>
+          <t>['실적 발표', '외국인 매수', '주가 상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14950</v>
+        <v>14940</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.12%</t>
+          <t>'+9.05%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F7" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G7" t="n">
-        <v>709</v>
+        <v>733</v>
       </c>
       <c r="H7" t="n">
         <v>2.87</v>
@@ -1070,7 +1070,7 @@
         <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>171779051510</v>
+        <v>172646547805</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미래 기술(메타 유리기판, 해상광통신) 및 AI 수요 관련 뉴스와 외국인 프로그램 매수를 근거로 긍정적 전망. 공매도 세력에 대한 경계 언급.</t>
+          <t>국민연금의 광통신 섹터 매수 및 AI 수요 증가 기대. 메타 유리기판, 해상광통신 케이블 등 신규 기술 성장성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI', '유리기판', '외국인']</t>
+          <t>['AI 수요', '광통신', '메타']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>241500</v>
+        <v>241250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.78%</t>
+          <t>'+8.67%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="G8" t="n">
-        <v>1619</v>
+        <v>1637</v>
       </c>
       <c r="H8" t="n">
         <v>46.15</v>
@@ -1162,7 +1162,7 @@
         <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3219819146250</v>
+        <v>3310120565250</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>노무라 증권 목표가 하향에도 불구하고, 3분기 순이익 예상치 및 자사주 소각 기대감 언급. 다만, 객관적 근거 부족으로 fact_score는 보수적으로 평가.</t>
+          <t>주주환원 및 자사주 소각 기대감 속, TSMC 및 SK하이닉스와의 실적 비교 분석. 100만 전자 목표.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주소각', '실적발표', '목표가']</t>
+          <t>['주주환원', '자사주 소각', '실적 비교']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18490</v>
+        <v>19320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.19%</t>
+          <t>'+7.99%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
       <c r="E9" t="n">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="F9" t="n">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
-        <v>412</v>
+        <v>115</v>
       </c>
       <c r="H9" t="n">
-        <v>4.74</v>
+        <v>4.25</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17090</v>
+        <v>17890</v>
       </c>
       <c r="K9" t="n">
-        <v>19270</v>
+        <v>18250</v>
       </c>
       <c r="L9" t="n">
-        <v>20450</v>
+        <v>20000</v>
       </c>
       <c r="M9" t="n">
-        <v>18070</v>
+        <v>17950</v>
       </c>
       <c r="N9" t="n">
-        <v>4.13</v>
+        <v>3.79</v>
       </c>
       <c r="O9" t="n">
-        <v>46527923315</v>
+        <v>71478748335</v>
       </c>
       <c r="P9" t="n">
-        <v>28600</v>
+        <v>22450</v>
       </c>
       <c r="Q9" t="n">
-        <v>11050</v>
+        <v>6320</v>
       </c>
       <c r="R9" t="n">
-        <v>-59000</v>
+        <v>-7000</v>
       </c>
       <c r="S9" t="n">
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>아틀라스 발주, 로봇 눈 공개, AI 데이터센터 방열 시스템 공급 계약 등 다수의 호재를 기반으로 한 강한 상승 기대감. 휴머노이드 로봇 산업 성장과 연계.</t>
+          <t>국내외 해킹 사고 연이은 발생, 양자보안 의무화 등 보안 섹터 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['로봇', 'AI', '휴머노이드']</t>
+          <t>['보안', '해킹', '양자보안']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19260</v>
+        <v>18370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.66%</t>
+          <t>'+7.49%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="E10" t="n">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="G10" t="n">
-        <v>112</v>
+        <v>415</v>
       </c>
       <c r="H10" t="n">
-        <v>4.25</v>
+        <v>4.74</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,139 +1331,139 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17890</v>
+        <v>17090</v>
       </c>
       <c r="K10" t="n">
-        <v>18250</v>
+        <v>19270</v>
       </c>
       <c r="L10" t="n">
-        <v>20000</v>
+        <v>20450</v>
       </c>
       <c r="M10" t="n">
-        <v>17950</v>
+        <v>18070</v>
       </c>
       <c r="N10" t="n">
-        <v>3.79</v>
+        <v>4.13</v>
       </c>
       <c r="O10" t="n">
-        <v>71118719595</v>
+        <v>46659341705</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>28600</v>
       </c>
       <c r="Q10" t="n">
-        <v>6320</v>
+        <v>11050</v>
       </c>
       <c r="R10" t="n">
-        <v>-7000</v>
+        <v>-59000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>국내외 해킹 사고 연이은 발생, 양자보안 의무화 등 보안 섹터 상승 기대.</t>
+          <t>아틀라스 발주, 로봇 눈 공개, AI 데이터센터 방열 시스템 공급 계약 등 다수의 호재를 기반으로 한 강한 상승 기대감. 휴머노이드 로봇 산업 성장과 연계.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '양자보안']</t>
+          <t>['로봇', 'AI', '휴머노이드']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2615</v>
+        <v>9250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+6.73%</t>
+          <t>'+7.18%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.68</v>
+        <v>0.13</v>
       </c>
       <c r="E11" t="n">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="F11" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G11" t="n">
-        <v>161</v>
+        <v>316</v>
       </c>
       <c r="H11" t="n">
-        <v>1.69</v>
+        <v>5.47</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2450</v>
+        <v>8630</v>
       </c>
       <c r="K11" t="n">
-        <v>2525</v>
+        <v>8660</v>
       </c>
       <c r="L11" t="n">
-        <v>2965</v>
+        <v>9410</v>
       </c>
       <c r="M11" t="n">
-        <v>2505</v>
+        <v>8410</v>
       </c>
       <c r="N11" t="n">
-        <v>1.01</v>
+        <v>5.34</v>
       </c>
       <c r="O11" t="n">
-        <v>87073405982</v>
+        <v>24812240315</v>
       </c>
       <c r="P11" t="n">
-        <v>2965</v>
+        <v>14940</v>
       </c>
       <c r="Q11" t="n">
-        <v>865</v>
+        <v>5390</v>
       </c>
       <c r="R11" t="n">
-        <v>-364000</v>
+        <v>1000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>거래량 증가 및 외국인 매수세 유입을 근거로 긍정적 전망 제시. 개인 물량 흡수 및 시세 분출 기대감 언급.</t>
+          <t>테슬라 로보택시 상표 등록 관련 호재. 공매도 세력과의 공방 속 주가 부양 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['거래량', '외국인', '손바뀜']</t>
+          <t>['테슬라', '로보택시', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,86 +1476,86 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9170</v>
+        <v>8590</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+6.26%</t>
+          <t>'+4.76%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.13</v>
+        <v>0.27</v>
       </c>
       <c r="E12" t="n">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="F12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G12" t="n">
-        <v>259</v>
+        <v>104</v>
       </c>
       <c r="H12" t="n">
-        <v>5.47</v>
+        <v>1.42</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8630</v>
+        <v>8200</v>
       </c>
       <c r="K12" t="n">
-        <v>8660</v>
+        <v>8230</v>
       </c>
       <c r="L12" t="n">
-        <v>9190</v>
+        <v>9780</v>
       </c>
       <c r="M12" t="n">
-        <v>8410</v>
+        <v>8100</v>
       </c>
       <c r="N12" t="n">
-        <v>5.34</v>
+        <v>1.15</v>
       </c>
       <c r="O12" t="n">
-        <v>19609399785</v>
+        <v>125854491355</v>
       </c>
       <c r="P12" t="n">
-        <v>14940</v>
+        <v>9820</v>
       </c>
       <c r="Q12" t="n">
-        <v>5390</v>
+        <v>2965</v>
       </c>
       <c r="R12" t="n">
-        <v>1000</v>
+        <v>-57000</v>
       </c>
       <c r="S12" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>테슬라 로보택시 관련 뉴스 언급에도 불구하고, 낮은 주가 상승률 및 공매도 관련 부정적 의견이 많음. 주가 상승 동력 부족.</t>
+          <t>미국 양자/보안주 급등 및 국내 해킹 사고 관련, 보안 테마 상승 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '로보택시', '주가']</t>
+          <t>['보안', '해킹', '테마']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,43 +1563,43 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8670</v>
+        <v>2565</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+5.73%</t>
+          <t>'+4.69%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.27</v>
+        <v>0.68</v>
       </c>
       <c r="E13" t="n">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="F13" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G13" t="n">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="H13" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8200</v>
+        <v>2450</v>
       </c>
       <c r="K13" t="n">
-        <v>8230</v>
+        <v>2525</v>
       </c>
       <c r="L13" t="n">
-        <v>9780</v>
+        <v>2965</v>
       </c>
       <c r="M13" t="n">
-        <v>8100</v>
+        <v>2505</v>
       </c>
       <c r="N13" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="O13" t="n">
-        <v>125291043155</v>
+        <v>88427075485</v>
       </c>
       <c r="P13" t="n">
-        <v>9820</v>
+        <v>2965</v>
       </c>
       <c r="Q13" t="n">
-        <v>2965</v>
+        <v>865</v>
       </c>
       <c r="R13" t="n">
-        <v>-57000</v>
+        <v>-364000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 양자/보안주 급등 및 국내 해킹 사고 관련, 보안 테마 상승 기대.</t>
+          <t>거래량 증가 및 외국인 매수세 유입을 근거로 긍정적 전망 제시. 개인 물량 흡수 및 시세 분출 기대감 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '테마']</t>
+          <t>['거래량', '외국인', '손바뀜']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>0.57</v>
       </c>
       <c r="E14" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F14" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G14" t="n">
-        <v>800</v>
+        <v>823</v>
       </c>
       <c r="H14" t="n">
         <v>41.01</v>
@@ -1714,7 +1714,7 @@
         <v>40.44</v>
       </c>
       <c r="O14" t="n">
-        <v>227695405200</v>
+        <v>232642093400</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>이란 최고지도자 발언 이후 전쟁 종식 기대감 속, 최근 4일간 코스피 수익률 1위 달성. 자사주 매입 및 공매도 세력과의 대결 구도로 인한 긍정적 전망.</t>
+          <t>최근 4일간 코스피 수익률 1위 달성 및 자사주 매입 지속. 공매도 세력에 대한 경계.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주 매입', '공매도', '이란 최고지도자']</t>
+          <t>['자사주 매입', '수익률', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>178250</v>
+        <v>178200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.27%</t>
+          <t>'+2.24%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G15" t="n">
-        <v>2544</v>
+        <v>2494</v>
       </c>
       <c r="H15" t="n">
         <v>35.43</v>
@@ -1806,7 +1806,7 @@
         <v>35.49</v>
       </c>
       <c r="O15" t="n">
-        <v>168883191650</v>
+        <v>173139129500</v>
       </c>
       <c r="P15" t="n">
         <v>304000</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>엔비디아 지분 투자 및 글로벌 전기차 부품 공급 관련 언급에도 불구하고, 주가 부진에 대한 불만 표출. 외국인 및 연기금 매도세 지적.</t>
+          <t>타 종목 대비 저조한 주가 흐름에 대한 불만. 공매도 비율 및 외국인, 연기금 매도세 지적.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['지분투자', '주가부진', '매도세']</t>
+          <t>['공매도', '외국인 매도', '주가 부진']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30000</v>
+        <v>29900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.69%</t>
+          <t>'+1.36%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F16" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G16" t="n">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="H16" t="n">
         <v>28.81</v>
@@ -1898,7 +1898,7 @@
         <v>28.82</v>
       </c>
       <c r="O16" t="n">
-        <v>34034339400</v>
+        <v>34744504875</v>
       </c>
       <c r="P16" t="n">
         <v>69700</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16500</v>
+        <v>16490</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+0.61%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G17" t="n">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H17" t="n">
         <v>28.03</v>
@@ -1990,7 +1990,7 @@
         <v>27.96</v>
       </c>
       <c r="O17" t="n">
-        <v>57264675820</v>
+        <v>58675143650</v>
       </c>
       <c r="P17" t="n">
         <v>35350</v>
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52500</v>
+        <v>14320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.94%</t>
+          <t>'-0.90%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.03</v>
+        <v>-0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>495</v>
+        <v>273</v>
       </c>
       <c r="F18" t="n">
-        <v>273</v>
+        <v>122</v>
       </c>
       <c r="G18" t="n">
-        <v>1313</v>
+        <v>672</v>
       </c>
       <c r="H18" t="n">
-        <v>10.31</v>
+        <v>9.83</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>53000</v>
+        <v>14450</v>
       </c>
       <c r="K18" t="n">
-        <v>53400</v>
+        <v>14750</v>
       </c>
       <c r="L18" t="n">
-        <v>53800</v>
+        <v>14870</v>
       </c>
       <c r="M18" t="n">
-        <v>51200</v>
+        <v>14090</v>
       </c>
       <c r="N18" t="n">
-        <v>10.34</v>
+        <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>81649195900</v>
+        <v>65289813885</v>
       </c>
       <c r="P18" t="n">
-        <v>154800</v>
+        <v>40350</v>
       </c>
       <c r="Q18" t="n">
-        <v>51200</v>
+        <v>3320</v>
       </c>
       <c r="R18" t="n">
-        <v>-412000</v>
+        <v>-839000</v>
       </c>
       <c r="S18" t="n">
-        <v>-70000</v>
+        <v>-141000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>코스피 대세 상승 및 미국 정상회담 기대감에도 불구하고 주가 하락. 조선업 협력 난항 및 과거 실적 부진으로 인한 투자 심리 위축.</t>
+          <t>코스피 지수 상승에도 하락한 주가에 대한 불만. 영업이익 증가와 주가 하락 간의 괴리 지적.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['조선업', '실적 부진', '투자 심리']</t>
+          <t>['영업이익', '주가 하락', '경영진']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>042660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14280</v>
+        <v>52300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-1.18%</t>
+          <t>'-1.32%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="E19" t="n">
-        <v>271</v>
+        <v>498</v>
       </c>
       <c r="F19" t="n">
-        <v>121</v>
+        <v>274</v>
       </c>
       <c r="G19" t="n">
-        <v>653</v>
+        <v>1343</v>
       </c>
       <c r="H19" t="n">
-        <v>9.83</v>
+        <v>10.31</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14450</v>
+        <v>53000</v>
       </c>
       <c r="K19" t="n">
-        <v>14750</v>
+        <v>53400</v>
       </c>
       <c r="L19" t="n">
-        <v>14870</v>
+        <v>53800</v>
       </c>
       <c r="M19" t="n">
-        <v>14090</v>
+        <v>51200</v>
       </c>
       <c r="N19" t="n">
-        <v>10.02</v>
+        <v>10.34</v>
       </c>
       <c r="O19" t="n">
-        <v>64317724835</v>
+        <v>82840555900</v>
       </c>
       <c r="P19" t="n">
-        <v>40350</v>
+        <v>154800</v>
       </c>
       <c r="Q19" t="n">
-        <v>3320</v>
+        <v>51200</v>
       </c>
       <c r="R19" t="n">
-        <v>-839000</v>
+        <v>-412000</v>
       </c>
       <c r="S19" t="n">
-        <v>-141000</v>
+        <v>-70000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>코스피 상승장 속 하락하며 상폐 및 경영진 비판 등 부정적 의견 다수. 영업이익 증가에도 주가 하락에 대한 의문 제기.</t>
+          <t>코스피 지수 상승에도 불구하고 주가 하락에 대한 불만. 실적 발표 후 주가 하락 반복 지적.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['상폐', '경영진', '영업이익']</t>
+          <t>['실적 발표', '주가 하락', '코스피']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>042660</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2040</v>
+        <v>2055</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.16%</t>
+          <t>'-1.44%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.39</v>
       </c>
       <c r="E20" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F20" t="n">
         <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H20" t="n">
         <v>2.52</v>
@@ -2257,7 +2257,7 @@
         <v>2005</v>
       </c>
       <c r="L20" t="n">
-        <v>2055</v>
+        <v>2060</v>
       </c>
       <c r="M20" t="n">
         <v>1805</v>
@@ -2266,7 +2266,7 @@
         <v>2.13</v>
       </c>
       <c r="O20" t="n">
-        <v>16273051571</v>
+        <v>16592950351</v>
       </c>
       <c r="P20" t="n">
         <v>6190</v>
@@ -2315,21 +2315,21 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2080</v>
+        <v>2085</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-4.15%</t>
+          <t>'-3.92%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.18</v>
       </c>
       <c r="E21" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
         <v>386</v>
@@ -2358,7 +2358,7 @@
         <v>4.89</v>
       </c>
       <c r="O21" t="n">
-        <v>51680627055</v>
+        <v>52136312520</v>
       </c>
       <c r="P21" t="n">
         <v>4980</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9010</v>
+        <v>9020</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-5.46%</t>
+          <t>'-5.35%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2424,7 +2424,7 @@
         <v>56</v>
       </c>
       <c r="G22" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="H22" t="n">
         <v>3.46</v>
@@ -2450,7 +2450,7 @@
         <v>2.63</v>
       </c>
       <c r="O22" t="n">
-        <v>45600415155</v>
+        <v>46066355855</v>
       </c>
       <c r="P22" t="n">
         <v>11690</v>
